--- a/plantilla_prueba.xlsx
+++ b/plantilla_prueba.xlsx
@@ -1,137 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FDA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66ED78C6-B913-4C8C-A020-9FF1C9BAA751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Estudiantes" sheetId="1" r:id="rId1"/>
+    <sheet name="Estudiantes_Reales" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
-  <si>
-    <t>ID_ESTUDIANTE</t>
-  </si>
-  <si>
-    <t>NOMBRE_COMPLETO</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANGULO VERTEL MATEO </t>
-  </si>
-  <si>
-    <t>mangulov@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BULA ESQUIVEL SEBASTIAN </t>
-  </si>
-  <si>
-    <t>sbulae@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>CALDERIN CABEZA DUVAN FELIPE</t>
-  </si>
-  <si>
-    <t>dfcalderin@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>CASTILLO CALDERA GEOVANYS STIVEN</t>
-  </si>
-  <si>
-    <t>gcastillo@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>GALARCIO HORTA DANIEL RAFAEL</t>
-  </si>
-  <si>
-    <t>drgalarcio@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOMEZ TIRADO ESTIVEN </t>
-  </si>
-  <si>
-    <t>egomezt@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>KELSY GALVAN ALEJANDRO JAVIER</t>
-  </si>
-  <si>
-    <t>akelsy@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>MERCADO LUNA SEBASTIAN ANDRES</t>
-  </si>
-  <si>
-    <t>samercado@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>MIRANDA CASTILLO ISAAC DAVID</t>
-  </si>
-  <si>
-    <t>idmiranda@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>NEGRETE BERONA ESTEBAN DAVID</t>
-  </si>
-  <si>
-    <t>ednegrete@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMOS  LUIDYN </t>
-  </si>
-  <si>
-    <t>luidynramos@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>RICARDO ORTEGA LUIS MANUEL</t>
-  </si>
-  <si>
-    <t>lmanuelricardo@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>TORRES PERDOMO RODRIGO JOSE</t>
-  </si>
-  <si>
-    <t>rjosetorres@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>TRUJILLO PICO DIEGO JOSE</t>
-  </si>
-  <si>
-    <t>dtrujillo@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEGA SALAS BLEYDER </t>
-  </si>
-  <si>
-    <t>bvegas@correo.unicordoba.edu.co</t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="23">
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;\ #,##0;\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;\ #,##0.00;\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;XDR&quot;#,##0;\-&quot;XDR&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;XDR&quot;#,##0;[Red]\-&quot;XDR&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;XDR&quot;#,##0.00;\-&quot;XDR&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;XDR&quot;#,##0.00;[Red]\-&quot;XDR&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;XDR&quot;* #,##0_-;\-&quot;XDR&quot;* #,##0_-;_-&quot;XDR&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;XDR&quot;* #,##0.00_-;\-&quot;XDR&quot;* #,##0.00_-;_-&quot;XDR&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="#,##0\ &quot;€&quot;;\-#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="171" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00\ &quot;€&quot;;\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="173" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -161,21 +87,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -500,235 +418,188 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="str">
+        <v/>
+      </c>
+      <c r="B1" t="str">
+        <v>numero</v>
+      </c>
+      <c r="C1" t="str">
+        <v>nombre</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
         <v>1071352648</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
+      <c r="C2" t="str">
+        <v xml:space="preserve">ANGULO VERTEL MATEO </v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
         <v>1062432634</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
+      <c r="C3" t="str">
+        <v xml:space="preserve">BULA ESQUIVEL SEBASTIAN </v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
         <v>1062436272</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
+      <c r="C4" t="str">
+        <v>CALDERIN CABEZA DUVAN FELIPE</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
         <v>1062440322</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
+      <c r="C5" t="str">
+        <v>CASTILLO CALDERA GEOVANYS STIVEN</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
         <v>1068419885</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
+      <c r="C6" t="str">
+        <v>GALARCIO HORTA DANIEL RAFAEL</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
         <v>1062435636</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
+      <c r="C7" t="str">
+        <v xml:space="preserve">GOMEZ TIRADO ESTIVEN </v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
         <v>1067884838</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
+      <c r="C8" t="str">
+        <v>KELSY GALVAN ALEJANDRO JAVIER</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
         <v>1067879061</v>
       </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
+      <c r="C9" t="str">
+        <v>MERCADO LUNA SEBASTIAN ANDRES</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
         <v>1062963483</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
+      <c r="C10" t="str">
+        <v>MIRANDA CASTILLO ISAAC DAVID</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
         <v>1138024256</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12">
+      <c r="C11" t="str">
+        <v>NEGRETE BERONA ESTEBAN DAVID</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
         <v>1067864566</v>
       </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13">
+      <c r="C12" t="str">
+        <v xml:space="preserve">RAMOS  LUIDYN </v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
         <v>1068137774</v>
       </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14">
+      <c r="C13" t="str">
+        <v>RICARDO ORTEGA LUIS MANUEL</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
         <v>1062435646</v>
       </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15">
+      <c r="C14" t="str">
+        <v>TORRES PERDOMO RODRIGO JOSE</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
         <v>1098073006</v>
       </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16">
+      <c r="C15" t="str">
+        <v>TRUJILLO PICO DIEGO JOSE</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16" t="str">
         <v>1062962652</v>
       </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
-        <v>33</v>
+      <c r="C16" t="str">
+        <v xml:space="preserve">VEGA SALAS BLEYDER </v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B1:C1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>